--- a/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J226-ModaliteAccueil-ROR.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J226-ModaliteAccueil-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>05</t>
   </si>
   <si>
-    <t>Visite à domicile</t>
+    <t>Visite et soins à domicile</t>
   </si>
   <si>
     <t>06</t>
@@ -240,19 +240,13 @@
     <t>25</t>
   </si>
   <si>
-    <t>Relayage courte durée (quelques heures par jour)</t>
+    <t>Relayage courte durée (&lt; un jour)</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>Relayage longue durée (sur plusieurs jours)</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Soins à domicile</t>
+    <t>Relayage longue durée (&gt; un jour)</t>
   </si>
   <si>
     <t/>
@@ -523,7 +517,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -743,23 +737,15 @@
         <v>78</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>80</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
